--- a/fotolar/Erjeokum_2026_Sunum_Listesi.xlsx
+++ b/fotolar/Erjeokum_2026_Sunum_Listesi.xlsx
@@ -1,331 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Akademik Çalışma Klasörleri\Çalıştay\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C3B476-D328-43CB-B51C-951656989475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="5370" yWindow="1320" windowWidth="32710" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5370" yWindow="1320" windowWidth="32710" windowHeight="18040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
-  <si>
-    <t>"Erzincan Jeolojik ve Kültürel Miras" Çalıştayı</t>
-  </si>
-  <si>
-    <t>📅  18 Haziran (Perşembe) 2026</t>
-  </si>
-  <si>
-    <t>OTURUM 1 — ERZİNCAN-OTLUKBELİ OTURUMU</t>
-  </si>
-  <si>
-    <t>SAAT</t>
-  </si>
-  <si>
-    <t>BİLDİRİ BAŞLIĞI</t>
-  </si>
-  <si>
-    <t>SUNUM YAPAN</t>
-  </si>
-  <si>
-    <t>09:30 - 10:00</t>
-  </si>
-  <si>
-    <t>UNESCO Jeoparkları; Barış Çağrılarından Doğa Korumaya Geçiş</t>
-  </si>
-  <si>
-    <t>Nizamettin KAZANCI</t>
-  </si>
-  <si>
-    <t>10:00 - 10:30</t>
-  </si>
-  <si>
-    <t>Travertine and Calcareous Tufa: “Master Keys” in Geological and Cultural Heritage</t>
-  </si>
-  <si>
-    <t>Enrico CAPEZZUOLI</t>
-  </si>
-  <si>
-    <t>10:30 - 10:45  ☕ Çay / Kahve Arası</t>
-  </si>
-  <si>
-    <t>10:45 - 11:00</t>
-  </si>
-  <si>
-    <t>Otlukbeli Travertenlerinin Jeolojik-Kültürel Mirası ve Erzincan-Otlukbeli Jeopark Potansiyeli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yakup ÇELİK </t>
-  </si>
-  <si>
-    <t>11:00 - 11:15</t>
-  </si>
-  <si>
-    <t>Jeolojik Miras Envanter Çalışması Aşamaları</t>
-  </si>
-  <si>
-    <t>Yıldırım GÜNGÖR</t>
-  </si>
-  <si>
-    <t>11:15 - 11:30</t>
-  </si>
-  <si>
-    <t>Jeoçeşitlilik ve Çevresel Tehditler</t>
-  </si>
-  <si>
-    <t>Raif KANDEMİR</t>
-  </si>
-  <si>
-    <t>12:30 - 13:30  🍽️ Öğle Yemeği</t>
-  </si>
-  <si>
-    <t>OTURUM 2 — ERZİNCAN-ÇAĞLAYAN OTURUMU</t>
-  </si>
-  <si>
-    <t>Akarsu Sistemlerinin Doğal Arşivi: Gürlevik Şelalesi ve Jeomiras Potansiyeli</t>
-  </si>
-  <si>
-    <t>Ezher TAGLIASACCHI</t>
-  </si>
-  <si>
-    <t>Erzincan'ın Jeolojik Miras Alanlarına İlişkin Yeni Örnekler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali ERGEN </t>
-  </si>
-  <si>
-    <t>14:30 - 14:45</t>
-  </si>
-  <si>
-    <t>Polat Gölü'nün Jeolojik-Jeomorfolojik Önemi ve Jeomiras Potansiyeli</t>
-  </si>
-  <si>
-    <t>Mehmet Akif TAŞ</t>
-  </si>
-  <si>
-    <t>OTURUM 3 — ERZİNCAN-KEMALİYE OTURUMU</t>
-  </si>
-  <si>
-    <t>Erzincan'ın Biyoçeşitliliğinin Tarihsel Gelişimi ve Önemi: Kemaliye Prof. Dr. Ali Demirsoy Doğa Tarihi Müzesi</t>
-  </si>
-  <si>
-    <t>Ali DEMİRSOY</t>
-  </si>
-  <si>
-    <t>Coğrafya ve Tarih: 1473 Otlukbeli Savaşının Yerinin Tespiti ve Yol Güzergahları</t>
-  </si>
-  <si>
-    <t>Kenan İNAN</t>
-  </si>
-  <si>
-    <t>16:00 - 16:15</t>
-  </si>
-  <si>
-    <t>Kemaliye'nin Jeolojisi, Doğa Değerleri, Antropojenik Tehlikeler ve Koruma Statüsü</t>
-  </si>
-  <si>
-    <t>Eşref ATABEY</t>
-  </si>
-  <si>
-    <t>16:15 - 16:30</t>
-  </si>
-  <si>
-    <t>Jeoradar Işığında Erzincan Kalesi ve Kent Meydanı Civarındaki Yapılar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vedat GÜNGÖR </t>
-  </si>
-  <si>
-    <t>Erzincan'ın Somut Kültürel Miras Değerleri ve Coğrafi Koşullarla Bağlantısı</t>
-  </si>
-  <si>
-    <t>Fatih ORHAN</t>
-  </si>
-  <si>
-    <t>OTURUM 4 — ERZİNCAN ÜZÜMLÜ OTURUMU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatma Şişman TÜKEL </t>
-  </si>
-  <si>
-    <t>Pınar POLAT</t>
-  </si>
-  <si>
-    <t>Esence (Keşiş) Dağları'nda Buzul Jeomorfolojisinin Jeomiras Potansiyeli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mutlu SEVEN </t>
-  </si>
-  <si>
-    <t>14:45 - 15:00</t>
-  </si>
-  <si>
-    <t>15:00 - 15:15</t>
-  </si>
-  <si>
-    <t>15:15 - 15:30</t>
-  </si>
-  <si>
-    <t>11:30 - 11:45</t>
-  </si>
-  <si>
-    <t>15:30 - 15:45  ☕ Çay / Kahve Arası</t>
-  </si>
-  <si>
-    <t>Oturum Yürütücüleri: Yakup ÇELİK, Ezher TAGLIASACCHI</t>
-  </si>
-  <si>
-    <t>Oturum Yürütücüleri: Pınar POLAT, Yıldırım GÜNGÖR</t>
-  </si>
-  <si>
-    <t>Oturum Yürütücüleri: Nizamettin KAZANCI, Vedat KARADENİZ</t>
-  </si>
-  <si>
-    <t>Oturum Yürütücüleri: Ali ERGEN, Fatih ORHAN</t>
-  </si>
-  <si>
-    <t>Kuzey Anadolu Fayı'nın Magmatik İzlerinden Jeolojik Mirasa:
-Erzincan Volkan Konilerinin Jeokimyasal ve Petrojenetik Değerlendirmesi</t>
-  </si>
-  <si>
-    <t>13:30 - 13:45</t>
-  </si>
-  <si>
-    <t>13:45 - 14:00</t>
-  </si>
-  <si>
-    <t>14:00 - 14:15</t>
-  </si>
-  <si>
-    <t>14:15 - 14:30  ☕ Çay / Kahve Arası</t>
-  </si>
-  <si>
-    <t>15:45 - 16:00</t>
-  </si>
-  <si>
-    <t>Konarlı Şelalesi (Tercan) İlk Bulgular ve Jeoturizm Potansiyeli</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="11">
     <font>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1B3A5C"/>
       <sz val="16"/>
-      <color rgb="FF1B3A5C"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF4A2D7A"/>
       <sz val="10"/>
-      <color rgb="FF4A2D7A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1B3A5C"/>
       <sz val="10"/>
-      <color rgb="FF1B3A5C"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <color rgb="FF333333"/>
       <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF333333"/>
       <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF2980B9"/>
       <sz val="10"/>
-      <color rgb="FF2980B9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF8E6E3C"/>
       <sz val="10"/>
-      <color rgb="FF8E6E3C"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1A6B3C"/>
       <sz val="10"/>
-      <color rgb="FF1A6B3C"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="17">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -713,141 +507,200 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="41">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1136,383 +989,522 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="525" row="2">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{FE829AEC-FCA5-4B1E-BCD2-F47B5B261418}">
-  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="claude.fileId" value="&quot;b3ad82eb-a50c-4650-adc8-8a3a683870bc&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="56.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="80.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.81640625" customWidth="1"/>
-    <col min="11" max="11" width="48.36328125" customWidth="1"/>
+    <col width="56.6328125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="80.54296875" customWidth="1" min="2" max="2"/>
+    <col width="17.08984375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.81640625" customWidth="1" min="10" max="10"/>
+    <col width="48.36328125" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="34"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="37" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="34"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="38"/>
-    </row>
-    <row r="24" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="34"/>
-    </row>
-    <row r="25" spans="1:3" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="34"/>
-    </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="34"/>
-    </row>
-    <row r="32" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="38"/>
-    </row>
-    <row r="33" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="34"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="34"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C40" s="18"/>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>"Erzincan Jeolojik ve Kültürel Miras" Çalıştayı</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>📅  18 Haziran (Perşembe) 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="15.5" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>OTURUM 1 — ERZİNCAN-OTLUKBELİ OTURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24.5" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri: Yakup ÇELİK, Ezher TAGLIASACCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>09:30 - 10:00</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>UNESCO Jeoparkları; Barış Çağrılarından Doğa Korumaya Geçiş</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Nizamettin KAZANCI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>10:00 - 10:30</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Travertine and Calcareous Tufa: “Master Keys” in Geological and Cultural Heritage</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>Enrico CAPEZZUOLI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20.5" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>10:30 - 10:45  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>10:45 - 11:00</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Otlukbeli Travertenlerinin Jeolojik-Kültürel Mirası ve Erzincan-Otlukbeli Jeopark Potansiyeli</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yakup ÇELİK </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>11:00 - 11:15</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Coğrafya ve Tarih: 1473 Otlukbeli Savaşının Yerinin Tespiti ve Yol Güzergahları</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>Kenan İNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>11:15 - 11:30</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Jeolojik Miras Envanter Çalışması Aşamaları</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>Yıldırım GÜNGÖR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>11:30 - 11:45</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Jeoçeşitlilik ve Çevresel Tehditler</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>Raif KANDEMİR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12:30 - 13:30  🍽️ Öğle Yemeği</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="8" customHeight="1">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>OTURUM 2 — ERZİNCAN-ÇAĞLAYAN OTURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri: Pınar POLAT, Yıldırım GÜNGÖR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>13:30 - 13:45</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Akarsu Sistemlerinin Doğal Arşivi: Gürlevik Şelalesi ve Jeomiras Potansiyeli</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>Ezher TAGLIASACCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>13:45 - 14:00</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Erzincan'ın Jeolojik Miras Alanlarına İlişkin Yeni Örnekler</t>
+        </is>
+      </c>
+      <c r="C20" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ali ERGEN </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>14:00 - 14:15</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Polat Gölü'nün Jeolojik-Jeomorfolojik Önemi ve Jeomiras Potansiyeli</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>Mehmet Akif TAŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>14:15 - 14:30  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="38" t="n"/>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>OTURUM 3 — ERZİNCAN-KEMALİYE OTURUMU</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="n"/>
+    </row>
+    <row r="25" ht="20.5" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri: Nizamettin KAZANCI, Vedat KARADENİZ</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>14:30 - 15:00</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Erzincan'ın Biyoçeşitliliğinin Tarihsel Gelişimi ve Önemi: Kemaliye Prof. Dr. Ali Demirsoy Doğa Tarihi Müzesi</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>Ali DEMİRSOY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>15:00 - 15:30</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Kemaliye'nin Jeolojisi, Doğa Değerleri, Antropojenik Tehlikeler ve Koruma Statüsü</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>Eşref ATABEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>15:30 - 15:45</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Jeoradar Işığında Erzincan Kalesi ve Kent Meydanı Civarındaki Yapılar</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vedat GÜNGÖR </t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>15:45 - 16:00</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Erzincan'ın Somut Kültürel Miras Değerleri ve Coğrafi Koşullarla Bağlantısı</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>Fatih ORHAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="inlineStr">
+        <is>
+          <t>16:00 - 16:15  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="1" t="n"/>
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="38" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>OTURUM 4 — ERZİNCAN ÜZÜMLÜ OTURUMU</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="n"/>
+    </row>
+    <row r="34" ht="15.5" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri: Ali ERGEN, Fatih ORHAN</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>16:15 - 16:30</t>
+        </is>
+      </c>
+      <c r="B36" s="40" t="inlineStr">
+        <is>
+          <t>Kuzey Anadolu Fayı'nın Magmatik İzlerinden Jeolojik Mirasa:
+Erzincan Volkan Konilerinin Jeokimyasal ve Petrojenetik Değerlendirmesi</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatma Şişman TÜKEL </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>16:30 - 16:45</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Konarlı Şelalesi (Tercan) İlk Bulgular ve Jeoturizm Potansiyeli</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>Pınar POLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>16:45 - 17:00</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Esence (Keşiş) Dağları'nda Buzul Jeomorfolojisinin Jeomiras Potansiyeli</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mutlu SEVEN </t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="1" t="n"/>
+    </row>
+    <row r="40">
+      <c r="C40" s="18" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" verticalDpi="1200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
